--- a/201025_Results_Cali/output/m2/21102025_mod2_by_gender.xlsx
+++ b/201025_Results_Cali/output/m2/21102025_mod2_by_gender.xlsx
@@ -2676,21 +2676,21 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Compras y trámites</t>
+          <t>Estudio</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>22 (10.4%)</t>
+          <t>9 (4.2%)</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>33 (14.9%)</t>
+          <t>13 (5.9%)</t>
         </is>
       </c>
       <c r="F78">
-        <v>0.0164</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="79">
@@ -2706,21 +2706,21 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cuidado y familia (centro educativo, niños/as o jóvenes)</t>
+          <t>Otro</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>4 (1.9%)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>3 (1.4%)</t>
+          <t>1 (0.5%)</t>
         </is>
       </c>
       <c r="F79">
-        <v>0.0164</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="80">
@@ -2736,21 +2736,21 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Cuidado y familia (otro lugar, niños/as o jóvenes)</t>
+          <t>Recreación y actividades personales</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>0 (0.0%)</t>
+          <t>12 (5.7%)</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>1 (0.5%)</t>
+          <t>5 (2.3%)</t>
         </is>
       </c>
       <c r="F80">
-        <v>0.0164</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="81">
@@ -2766,21 +2766,21 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Estudio</t>
+          <t>Salud</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>9 (4.2%)</t>
+          <t>24 (11.3%)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>13 (5.9%)</t>
+          <t>53 (24.0%)</t>
         </is>
       </c>
       <c r="F81">
-        <v>0.0164</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="82">
@@ -2796,21 +2796,21 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Otro</t>
+          <t>Trabajo</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4 (1.9%)</t>
+          <t>136 (64.2%)</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>1 (0.5%)</t>
+          <t>107 (48.4%)</t>
         </is>
       </c>
       <c r="F82">
-        <v>0.0164</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="83">
@@ -2826,21 +2826,21 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Recreación, salud y actividades personales</t>
+          <t>Trámites</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>36 (17.0%)</t>
+          <t>6 (2.8%)</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>58 (26.2%)</t>
+          <t>11 (5.0%)</t>
         </is>
       </c>
       <c r="F83">
-        <v>0.0164</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="84">
@@ -2856,21 +2856,21 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Trabajo</t>
+          <t>Viajes de cuidado</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>136 (64.2%)</t>
+          <t>16 (7.5%)</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>107 (48.4%)</t>
+          <t>26 (11.8%)</t>
         </is>
       </c>
       <c r="F84">
-        <v>0.0164</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="85">
@@ -2900,7 +2900,7 @@
         </is>
       </c>
       <c r="F85">
-        <v>0.0164</v>
+        <v>0.0014</v>
       </c>
     </row>
     <row r="86">
